--- a/stories/arbres/TREE-SEC-030.xlsx
+++ b/stories/arbres/TREE-SEC-030.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Sara est avec maman, à la maison. Sara a envie de jouer. maman est là, tout près. On va apprendre : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara écoute maman. Sara entend les mots : appeler un adulte, mains avec les jouets.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sara va vers le bac à sable. Un chat miaule une fois. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Sara se souvient : appeler un adulte, mains avec les jouets. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. On range un objet. maman dit : je suis là. On reste ensemble.</t>
+          <t>Sara va vers le bac à sable. Un chat miaule une fois. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Sara se souvient : appeler un adulte, mains avec les jouets. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. On range un objet. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1653,6 +1680,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Sara va vers le bac à sable. Un chat miaule une fois. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Sara se souvient : appeler un adulte, mains avec les jouets. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. On range un objet.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1866,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Les prises sont pour les adultes.</t>
         </is>
       </c>
     </row>
@@ -2005,6 +2043,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara respire. Sara retient : appeler un adulte, mains avec les jouets. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2191,6 +2234,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2357,6 +2405,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi les cubes. La couverture est douce. Les cubes reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara répète tout bas : appeler un adulte, mains avec les jouets. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2543,6 +2596,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2709,6 +2767,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin. Le vent est doux. On range un objet. Cette fin-là est celle de le bac à sable, les cubes et le matin. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2871,6 +2934,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3037,6 +3105,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le bac à sable, les cubes et après la sieste. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3199,6 +3272,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3365,6 +3443,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le bac à sable, les cubes et le soir. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3527,6 +3610,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3693,6 +3781,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le livre. On entend un oiseau. Le livre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara répète tout bas : appeler un adulte, mains avec les jouets. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3879,6 +3972,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4045,6 +4143,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin. Le sol est un peu froid. On range un objet. Cette fin-là est celle de le bac à sable, le livre et le matin. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4207,6 +4310,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4373,6 +4481,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste. Une feuille tombe. On dit merci. Cette fin-là est celle de le bac à sable, le livre et après la sieste. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4535,6 +4648,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4701,6 +4819,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le bac à sable, le livre et le soir. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4863,6 +4986,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5029,6 +5157,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi la dînette. Ça sent le pain chaud. La dînette reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara répète tout bas : appeler un adulte, mains avec les jouets. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5215,6 +5348,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5381,6 +5519,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin. Une feuille tombe. On range un objet. Cette fin-là est celle de le bac à sable, la dînette et le matin. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5543,6 +5686,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5709,6 +5857,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le bac à sable, la dînette et après la sieste. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5871,6 +6024,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6037,6 +6195,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le bac à sable, la dînette et le soir. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6199,6 +6362,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6223,7 +6391,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Sara va vers le toboggan. Les chaussures font toc toc. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Sara se souvient : appeler un adulte, mains avec les jouets. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. On dit merci. maman dit : je suis là. On reste ensemble.</t>
+          <t>Sara va vers le toboggan. Les chaussures font toc toc. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Sara se souvient : appeler un adulte, mains avec les jouets. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. On dit merci. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6365,6 +6533,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Sara va vers le toboggan. Les chaussures font toc toc. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Sara se souvient : appeler un adulte, mains avec les jouets. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. On dit merci.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6545,6 +6719,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Les prises sont pour les adultes.</t>
         </is>
       </c>
     </row>
@@ -6717,6 +6896,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara respire. Sara retient : appeler un adulte, mains avec les jouets. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6903,6 +7087,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7069,6 +7258,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi les cubes. Le vent est doux. Les cubes reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara répète tout bas : appeler un adulte, mains avec les jouets. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7255,6 +7449,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7421,6 +7620,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le toboggan, les cubes et le matin. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7583,6 +7787,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7749,6 +7958,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le toboggan, les cubes et après la sieste. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7911,6 +8125,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8077,6 +8296,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, les cubes et le soir. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8239,6 +8463,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8405,6 +8634,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le livre. Le sol est un peu froid. Le livre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara répète tout bas : appeler un adulte, mains avec les jouets. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8591,6 +8825,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8757,6 +8996,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin. Une feuille tombe. On dit merci. Cette fin-là est celle de le toboggan, le livre et le matin. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8919,6 +9163,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9085,6 +9334,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le toboggan, le livre et après la sieste. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9247,6 +9501,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9413,6 +9672,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le livre et le soir. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9575,6 +9839,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9741,6 +10010,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi la dînette. Une feuille tombe. La dînette reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara répète tout bas : appeler un adulte, mains avec les jouets. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9927,6 +10201,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10093,6 +10372,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le toboggan, la dînette et le matin. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10255,6 +10539,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10421,6 +10710,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le toboggan, la dînette et après la sieste. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10583,6 +10877,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10749,6 +11048,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, la dînette et le soir. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10911,6 +11215,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10935,7 +11244,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Sara va vers les balançoires. La couverture est douce. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Sara se souvient : appeler un adulte, mains avec les jouets. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. On souffle doucement. maman dit : je suis là. On reste ensemble.</t>
+          <t>Sara va vers les balançoires. La couverture est douce. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Sara se souvient : appeler un adulte, mains avec les jouets. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. On souffle doucement. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11077,6 +11386,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Sara va vers les balançoires. La couverture est douce. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Sara se souvient : appeler un adulte, mains avec les jouets. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. On souffle doucement.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11257,6 +11572,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Les prises sont pour les adultes.</t>
         </is>
       </c>
     </row>
@@ -11429,6 +11749,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara respire. Sara retient : appeler un adulte, mains avec les jouets. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11615,6 +11940,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11781,6 +12111,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi les cubes. L'eau coule, tout petit bruit. Les cubes reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara répète tout bas : appeler un adulte, mains avec les jouets. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11967,6 +12302,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12133,6 +12473,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin. Une feuille tombe. On souffle doucement. Cette fin-là est celle de les balançoires, les cubes et le matin. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12295,6 +12640,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12461,6 +12811,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, les cubes et après la sieste. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12623,6 +12978,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12789,6 +13149,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de les balançoires, les cubes et le soir. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12951,6 +13316,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13117,6 +13487,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le livre. Un vélo passe au loin. Le livre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara répète tout bas : appeler un adulte, mains avec les jouets. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13303,6 +13678,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13469,6 +13849,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de les balançoires, le livre et le matin. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13631,6 +14016,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13797,6 +14187,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le livre et après la sieste. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13959,6 +14354,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14125,6 +14525,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir. La lumière est claire. On attend son tour. Cette fin-là est celle de les balançoires, le livre et le soir. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14287,6 +14692,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14453,6 +14863,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi la dînette. La lumière est claire. La dînette reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara répète tout bas : appeler un adulte, mains avec les jouets. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14639,6 +15054,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14805,6 +15225,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de les balançoires, la dînette et le matin. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14967,6 +15392,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15133,6 +15563,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, la dînette et après la sieste. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15295,6 +15730,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15461,6 +15901,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de les balançoires, la dînette et le soir. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15623,6 +16068,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15641,7 +16091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15658,6 +16108,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SEC-030.xlsx
+++ b/stories/arbres/TREE-SEC-030.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Sara est avec maman, à la maison. Sara a envie de jouer. maman est là, tout près. On va apprendre : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara écoute maman. Sara entend les mots : appeler un adulte, mains avec les jouets.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1686,6 +1693,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1873,6 +1881,7 @@
           <t>narrateur|Que fait-on ? Les prises sont pour les adultes.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2048,6 +2057,7 @@
           <t>narrateur|Oui. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara respire. Sara retient : appeler un adulte, mains avec les jouets. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2239,6 +2249,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2410,6 +2421,7 @@
           <t>narrateur|Sara a choisi les cubes. La couverture est douce. Les cubes reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara répète tout bas : appeler un adulte, mains avec les jouets. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2601,6 +2613,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2772,6 +2785,7 @@
           <t>narrateur|Sara rejoint le matin. Le vent est doux. On range un objet. Cette fin-là est celle de le bac à sable, les cubes et le matin. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2939,6 +2953,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3110,6 +3125,7 @@
           <t>narrateur|Sara rejoint après la sieste. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le bac à sable, les cubes et après la sieste. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3277,6 +3293,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3448,6 +3465,7 @@
           <t>narrateur|Sara rejoint le soir. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le bac à sable, les cubes et le soir. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3615,6 +3633,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3786,6 +3805,7 @@
           <t>narrateur|Sara a choisi le livre. On entend un oiseau. Le livre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara répète tout bas : appeler un adulte, mains avec les jouets. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3977,6 +3997,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4148,6 +4169,7 @@
           <t>narrateur|Sara rejoint le matin. Le sol est un peu froid. On range un objet. Cette fin-là est celle de le bac à sable, le livre et le matin. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4315,6 +4337,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4486,6 +4509,7 @@
           <t>narrateur|Sara rejoint après la sieste. Une feuille tombe. On dit merci. Cette fin-là est celle de le bac à sable, le livre et après la sieste. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4653,6 +4677,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4824,6 +4849,7 @@
           <t>narrateur|Sara rejoint le soir. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le bac à sable, le livre et le soir. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4991,6 +5017,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5162,6 +5189,7 @@
           <t>narrateur|Sara a choisi la dînette. Ça sent le pain chaud. La dînette reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara répète tout bas : appeler un adulte, mains avec les jouets. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5353,6 +5381,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5524,6 +5553,7 @@
           <t>narrateur|Sara rejoint le matin. Une feuille tombe. On range un objet. Cette fin-là est celle de le bac à sable, la dînette et le matin. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5691,6 +5721,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5862,6 +5893,7 @@
           <t>narrateur|Sara rejoint après la sieste. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le bac à sable, la dînette et après la sieste. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6029,6 +6061,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6200,6 +6233,7 @@
           <t>narrateur|Sara rejoint le soir. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le bac à sable, la dînette et le soir. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6367,6 +6401,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6539,6 +6574,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6726,6 +6762,7 @@
           <t>narrateur|Que fait-on ? Les prises sont pour les adultes.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6901,6 +6938,7 @@
           <t>narrateur|Oui. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara respire. Sara retient : appeler un adulte, mains avec les jouets. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7092,6 +7130,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7263,6 +7302,7 @@
           <t>narrateur|Sara a choisi les cubes. Le vent est doux. Les cubes reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara répète tout bas : appeler un adulte, mains avec les jouets. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7454,6 +7494,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7625,6 +7666,7 @@
           <t>narrateur|Sara rejoint le matin. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le toboggan, les cubes et le matin. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7792,6 +7834,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7963,6 +8006,7 @@
           <t>narrateur|Sara rejoint après la sieste. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le toboggan, les cubes et après la sieste. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8130,6 +8174,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8301,6 +8346,7 @@
           <t>narrateur|Sara rejoint le soir. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, les cubes et le soir. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8468,6 +8514,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8639,6 +8686,7 @@
           <t>narrateur|Sara a choisi le livre. Le sol est un peu froid. Le livre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara répète tout bas : appeler un adulte, mains avec les jouets. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8830,6 +8878,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -9001,6 +9050,7 @@
           <t>narrateur|Sara rejoint le matin. Une feuille tombe. On dit merci. Cette fin-là est celle de le toboggan, le livre et le matin. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9168,6 +9218,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9339,6 +9390,7 @@
           <t>narrateur|Sara rejoint après la sieste. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le toboggan, le livre et après la sieste. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9506,6 +9558,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9677,6 +9730,7 @@
           <t>narrateur|Sara rejoint le soir. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le livre et le soir. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9844,6 +9898,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -10015,6 +10070,7 @@
           <t>narrateur|Sara a choisi la dînette. Une feuille tombe. La dînette reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara répète tout bas : appeler un adulte, mains avec les jouets. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10206,6 +10262,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10377,6 +10434,7 @@
           <t>narrateur|Sara rejoint le matin. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le toboggan, la dînette et le matin. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10544,6 +10602,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10715,6 +10774,7 @@
           <t>narrateur|Sara rejoint après la sieste. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le toboggan, la dînette et après la sieste. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10882,6 +10942,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11053,6 +11114,7 @@
           <t>narrateur|Sara rejoint le soir. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, la dînette et le soir. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11220,6 +11282,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11392,6 +11455,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11579,6 +11643,7 @@
           <t>narrateur|Que fait-on ? Les prises sont pour les adultes.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11754,6 +11819,7 @@
           <t>narrateur|Oui. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara respire. Sara retient : appeler un adulte, mains avec les jouets. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11945,6 +12011,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12116,6 +12183,7 @@
           <t>narrateur|Sara a choisi les cubes. L'eau coule, tout petit bruit. Les cubes reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara répète tout bas : appeler un adulte, mains avec les jouets. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12307,6 +12375,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12478,6 +12547,7 @@
           <t>narrateur|Sara rejoint le matin. Une feuille tombe. On souffle doucement. Cette fin-là est celle de les balançoires, les cubes et le matin. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12645,6 +12715,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12816,6 +12887,7 @@
           <t>narrateur|Sara rejoint après la sieste. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, les cubes et après la sieste. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12983,6 +13055,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13154,6 +13227,7 @@
           <t>narrateur|Sara rejoint le soir. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de les balançoires, les cubes et le soir. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13321,6 +13395,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13492,6 +13567,7 @@
           <t>narrateur|Sara a choisi le livre. Un vélo passe au loin. Le livre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara répète tout bas : appeler un adulte, mains avec les jouets. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13683,6 +13759,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13854,6 +13931,7 @@
           <t>narrateur|Sara rejoint le matin. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de les balançoires, le livre et le matin. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -14021,6 +14099,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14192,6 +14271,7 @@
           <t>narrateur|Sara rejoint après la sieste. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le livre et après la sieste. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14359,6 +14439,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14530,6 +14611,7 @@
           <t>narrateur|Sara rejoint le soir. La lumière est claire. On attend son tour. Cette fin-là est celle de les balançoires, le livre et le soir. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14697,6 +14779,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14868,6 +14951,7 @@
           <t>narrateur|Sara a choisi la dînette. La lumière est claire. La dînette reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara répète tout bas : appeler un adulte, mains avec les jouets. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -15059,6 +15143,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15230,6 +15315,7 @@
           <t>narrateur|Sara rejoint le matin. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de les balançoires, la dînette et le matin. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15397,6 +15483,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15568,6 +15655,7 @@
           <t>narrateur|Sara rejoint après la sieste. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, la dînette et après la sieste. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15735,6 +15823,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15906,6 +15995,7 @@
           <t>narrateur|Sara rejoint le soir. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de les balançoires, la dînette et le soir. Sara a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Sara a entendu : appeler un adulte, mains avec les jouets. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -16073,6 +16163,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16091,7 +16182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16115,6 +16206,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16129,7 +16234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16316,6 +16421,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
